--- a/Paranoid Android/Assets/Configs/ItemTable.xlsx
+++ b/Paranoid Android/Assets/Configs/ItemTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>ItemID</t>
   </si>
@@ -38,12 +38,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>PrefabAddress</t>
-  </si>
-  <si>
-    <t>IconAddress</t>
-  </si>
-  <si>
     <t>MaxStack</t>
   </si>
   <si>
@@ -53,15 +47,36 @@
     <t>ItemType</t>
   </si>
   <si>
+    <t>FireRate</t>
+  </si>
+  <si>
+    <t>LoadPerShot</t>
+  </si>
+  <si>
+    <t>BaseSpread</t>
+  </si>
+  <si>
+    <t>AimSpreadMult</t>
+  </si>
+  <si>
+    <t>AimSpeed</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>BulletSpeed</t>
+  </si>
+  <si>
+    <t>Distance</t>
+  </si>
+  <si>
     <t>Protoza</t>
   </si>
   <si>
     <t>Inital Weapon</t>
   </si>
   <si>
-    <t>ProtozaIcon</t>
-  </si>
-  <si>
     <t>Weapon</t>
   </si>
   <si>
@@ -71,36 +86,24 @@
     <t>Submachine Gun</t>
   </si>
   <si>
-    <t>Albus02Icon</t>
-  </si>
-  <si>
     <t>Scrawler</t>
   </si>
   <si>
     <t>Rifle</t>
   </si>
   <si>
-    <t>ScrawlerIcon</t>
-  </si>
-  <si>
     <t>Electris</t>
   </si>
   <si>
     <t>Sniper Rifle</t>
   </si>
   <si>
-    <t>ElectrisIcon</t>
-  </si>
-  <si>
     <t>SmallGena</t>
   </si>
   <si>
     <t>Small bullet Generator</t>
   </si>
   <si>
-    <t>SmallGenaIcon</t>
-  </si>
-  <si>
     <t>Loot</t>
   </si>
   <si>
@@ -110,16 +113,10 @@
     <t>Middle bullet Generator</t>
   </si>
   <si>
-    <t>MiddleGenaIcon</t>
-  </si>
-  <si>
     <t>LargeGena</t>
   </si>
   <si>
     <t>Large bullet Generator</t>
-  </si>
-  <si>
-    <t>LargeGenaIcon</t>
   </si>
 </sst>
 </file>
@@ -1264,18 +1261,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="2" width="13.1818181818182" customWidth="1"/>
     <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
-    <col min="4" max="4" width="20.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="18.1818181818182" customWidth="1"/>
+    <col min="4" max="4" width="10.7272727272727" customWidth="1"/>
     <col min="6" max="6" width="10.7272727272727" customWidth="1"/>
-    <col min="8" max="8" width="10.7272727272727" customWidth="1"/>
+    <col min="8" max="8" width="13.2727272727273" customWidth="1"/>
+    <col min="9" max="9" width="11.0909090909091" customWidth="1"/>
+    <col min="10" max="10" width="14.3636363636364" customWidth="1"/>
+    <col min="13" max="13" width="12.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1300,164 +1299,242 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2">
+        <v>15</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
+      <c r="E2">
+        <v>0.8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
       <c r="G2">
-        <v>0.8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
+        <v>4.5</v>
+      </c>
+      <c r="H2">
+        <v>0.5</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>0.7</v>
+      </c>
+      <c r="K2">
+        <v>0.4</v>
+      </c>
+      <c r="L2">
+        <v>12</v>
+      </c>
+      <c r="M2">
+        <v>12</v>
+      </c>
+      <c r="N2">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3">
+        <v>18</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
+      <c r="E3">
+        <v>2.8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
       <c r="G3">
-        <v>2.8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>1.5</v>
+      </c>
+      <c r="I3">
+        <v>3.3</v>
+      </c>
+      <c r="J3">
+        <v>0.5</v>
+      </c>
+      <c r="K3">
+        <v>0.6</v>
+      </c>
+      <c r="L3">
+        <v>25</v>
+      </c>
+      <c r="M3">
+        <v>15</v>
+      </c>
+      <c r="N3">
+        <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>1003</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>3.5</v>
+      </c>
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="G4">
-        <v>3.5</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>2.5</v>
+      </c>
+      <c r="I4">
+        <v>3.3</v>
+      </c>
+      <c r="J4">
+        <v>0.5</v>
+      </c>
+      <c r="K4">
+        <v>0.7</v>
+      </c>
+      <c r="L4">
+        <v>35</v>
+      </c>
+      <c r="M4">
+        <v>18</v>
+      </c>
+      <c r="N4">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5">
+        <v>22</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
+      <c r="E5">
+        <v>6.5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
       <c r="G5">
-        <v>6.5</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>0.4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>43</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2001</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6">
+        <v>24</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="G6">
+      <c r="E6">
         <v>0.2</v>
       </c>
-      <c r="H6" t="s">
-        <v>24</v>
+      <c r="F6" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>2002</v>
       </c>
       <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>0.3</v>
-      </c>
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>2003</v>
       </c>
@@ -1467,32 +1544,26 @@
       <c r="C8" t="s">
         <v>29</v>
       </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8">
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="G8">
+      <c r="E8">
         <v>0.5</v>
       </c>
-      <c r="H8" t="s">
-        <v>24</v>
+      <c r="F8" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
       <formula1>"Weapon,Ammo,Consumable,Loot"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="H1" listDataValidation="1"/>
+    <ignoredError sqref="F1" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Paranoid Android/Assets/Configs/ItemTable.xlsx
+++ b/Paranoid Android/Assets/Configs/ItemTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>ItemID</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>ItemType</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
   <si>
     <t>FireRate</t>
@@ -1261,20 +1264,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="2" width="13.1818181818182" customWidth="1"/>
     <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
     <col min="4" max="4" width="10.7272727272727" customWidth="1"/>
+    <col min="5" max="5" width="8.90909090909091" customWidth="1"/>
     <col min="6" max="6" width="10.7272727272727" customWidth="1"/>
-    <col min="8" max="8" width="13.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="11.0909090909091" customWidth="1"/>
-    <col min="10" max="10" width="14.3636363636364" customWidth="1"/>
-    <col min="13" max="13" width="12.6363636363636" customWidth="1"/>
+    <col min="9" max="9" width="13.2727272727273" customWidth="1"/>
+    <col min="10" max="10" width="11.0909090909091" customWidth="1"/>
+    <col min="11" max="11" width="14.3636363636364" customWidth="1"/>
+    <col min="14" max="14" width="12.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1317,16 +1321,19 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1335,42 +1342,45 @@
         <v>0.8</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2">
         <v>4.5</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.5</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>5</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.7</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.4</v>
-      </c>
-      <c r="L2">
-        <v>12</v>
       </c>
       <c r="M2">
         <v>12</v>
       </c>
       <c r="N2">
+        <v>12</v>
+      </c>
+      <c r="O2">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1379,42 +1389,45 @@
         <v>2.8</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3">
+        <v>500</v>
+      </c>
+      <c r="H3">
         <v>8</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1.5</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>3.3</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.5</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.6</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>25</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>15</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>1003</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1423,42 +1436,45 @@
         <v>3.5</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4">
+        <v>500</v>
+      </c>
+      <c r="H4">
         <v>6</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>2.5</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>3.3</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.5</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.7</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>35</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>18</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1467,42 +1483,45 @@
         <v>6.5</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5">
+        <v>500</v>
+      </c>
+      <c r="H5">
         <v>3</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>5</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>3</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.4</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>1</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>43</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>23</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>2001</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1511,18 +1530,21 @@
         <v>0.2</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>2002</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1531,18 +1553,21 @@
         <v>0.3</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="G7">
+        <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>2003</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1551,7 +1576,10 @@
         <v>0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Paranoid Android/Assets/Configs/ItemTable.xlsx
+++ b/Paranoid Android/Assets/Configs/ItemTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>ItemID</t>
   </si>
@@ -74,52 +74,73 @@
     <t>Distance</t>
   </si>
   <si>
+    <t>BulletType</t>
+  </si>
+  <si>
     <t>Protoza</t>
   </si>
   <si>
-    <t>Inital Weapon</t>
+    <t>一把粗制滥造的武器，只比没有武器好一些。</t>
   </si>
   <si>
     <t>Weapon</t>
   </si>
   <si>
+    <t>Normal</t>
+  </si>
+  <si>
     <t>Albus02</t>
   </si>
   <si>
-    <t>Submachine Gun</t>
+    <t>一把射速非常快的武器，缺点是散布较大以及射程较短。</t>
+  </si>
+  <si>
+    <t>Cube</t>
   </si>
   <si>
     <t>Scrawler</t>
   </si>
   <si>
-    <t>Rifle</t>
+    <t>一把很均衡的强力武器，是以旧日的军用武器为模板制作的。</t>
+  </si>
+  <si>
+    <t>Scarlet</t>
   </si>
   <si>
     <t>Electris</t>
   </si>
   <si>
-    <t>Sniper Rifle</t>
-  </si>
-  <si>
-    <t>SmallGena</t>
-  </si>
-  <si>
-    <t>Small bullet Generator</t>
+    <t>一把威力巨大的武器，但会对使用者造成很大负载。</t>
+  </si>
+  <si>
+    <t>Arrow</t>
+  </si>
+  <si>
+    <t>破损数据芯片</t>
+  </si>
+  <si>
+    <t>和垃圾没有太大区别，但总归能当作样品。</t>
   </si>
   <si>
     <t>Loot</t>
   </si>
   <si>
-    <t>MiddleGena</t>
-  </si>
-  <si>
-    <t>Middle bullet Generator</t>
-  </si>
-  <si>
-    <t>LargeGena</t>
-  </si>
-  <si>
-    <t>Large bullet Generator</t>
+    <t>数据芯片</t>
+  </si>
+  <si>
+    <t>能解析出大量数据的样品。</t>
+  </si>
+  <si>
+    <t>机密数据芯片</t>
+  </si>
+  <si>
+    <t>存储着重要军用数据的芯片，虽然破解很困难，但毫无疑问是最合适的样品之一。</t>
+  </si>
+  <si>
+    <t>清扫者的芯片</t>
+  </si>
+  <si>
+    <t>这是你击败了那个大家伙的奖章。当然，作为样品也非常合适。</t>
   </si>
 </sst>
 </file>
@@ -1264,11 +1285,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7"/>
+  <dimension ref="A1:P9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
+    <col min="3" max="3" width="73.7272727272727" customWidth="1"/>
     <col min="4" max="4" width="10.7272727272727" customWidth="1"/>
     <col min="5" max="5" width="8.90909090909091" customWidth="1"/>
     <col min="6" max="6" width="10.7272727272727" customWidth="1"/>
@@ -1278,7 +1299,7 @@
     <col min="14" max="14" width="12.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1324,16 +1345,19 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1342,45 +1366,48 @@
         <v>0.8</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>-1</v>
       </c>
       <c r="H2">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L2">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M2">
         <v>12</v>
       </c>
       <c r="N2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O2">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="P2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1389,45 +1416,48 @@
         <v>2.8</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>500</v>
+        <v>-1</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I3">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="K3">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L3">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M3">
+        <v>16</v>
+      </c>
+      <c r="N3">
+        <v>26</v>
+      </c>
+      <c r="O3">
         <v>25</v>
       </c>
-      <c r="N3">
-        <v>15</v>
-      </c>
-      <c r="O3">
-        <v>20</v>
+      <c r="P3" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>1003</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1436,45 +1466,48 @@
         <v>3.5</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>500</v>
+        <v>-1</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>2.5</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L4">
         <v>0.7</v>
       </c>
       <c r="M4">
+        <v>20</v>
+      </c>
+      <c r="N4">
+        <v>30</v>
+      </c>
+      <c r="O4">
         <v>35</v>
       </c>
-      <c r="N4">
-        <v>18</v>
-      </c>
-      <c r="O4">
-        <v>30</v>
+      <c r="P4" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1483,34 +1516,37 @@
         <v>6.5</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>500</v>
+        <v>-1</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M5">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="N5">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>80</v>
+      </c>
+      <c r="P5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1518,22 +1554,22 @@
         <v>2001</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>0.2</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1541,19 +1577,19 @@
         <v>2002</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>0.3</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -1564,27 +1600,50 @@
         <v>2003</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>2004</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F5 F6:F1048576">
       <formula1>"Weapon,Ammo,Consumable,Loot"</formula1>
     </dataValidation>
   </dataValidations>
